--- a/Backend/media/planillas_excel/ventas.xlsx
+++ b/Backend/media/planillas_excel/ventas.xlsx
@@ -431,12 +431,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -465,44 +465,8866 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-03 22:05:46</t>
+          <t>2026-10-24 16:17:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>45409.69233351899</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Tarjeta de debito</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>koch</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 15:15:40</t>
+          <t>2026-07-05 19:40:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>89539.28775230401</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-11 16:57:04</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>113708.6805412976</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-01 13:48:22</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>179171.0577278514</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24 23:10:42</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>77176.47957516879</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-09 14:53:35</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>223147.2773022395</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-16 10:07:44</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>282275.52545267565</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-07 18:11:16</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>82031.5230266232</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>admin</t>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:26:11</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>25498.0229636412</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 02:42:49</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>167167.78171449498</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08 08:35:53</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>251328.515939648</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02 18:24:46</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>116468.578685331</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07 17:14:32</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>117350.60404033618</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:16:50</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>167336.6542487616</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02 10:11:20</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>125637.8613577728</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-07 14:47:33</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>74854.8917288625</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 21:14:43</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>159044.47457815378</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24 21:10:47</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>144571.0242411</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06 06:57:39</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>173288.6431572528</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-12 10:08:23</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>78134.480985785</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-02 19:53:00</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>142715.97684420578</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:00:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>149744.9978707712</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-11 01:12:18</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>235308.85219664688</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-03 14:09:51</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>107399.8168663014</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19 09:25:27</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>21552.314946786</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-16 07:34:59</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>87823.81421647199</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-06 21:41:12</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>314133.3287797397</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-27 18:12:33</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>36518.0890894182</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:31:30</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>28826.6020794648</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 06:34:43</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>236677.172240672</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:39:16</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>33114.09476918881</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-03 17:02:12</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>13542.6164064384</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:10:00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>18903.335422112803</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:06:39</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>71120.4842293379</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-10 06:19:40</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>178718.52337569598</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-24 12:23:54</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>35229.95046476799</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20 13:34:15</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>87953.8651482612</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-10 09:36:08</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>215143.93678239002</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:17:22</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>38639.069071456004</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18 13:12:50</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>34958.46157359361</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 05:24:09</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>112236.6454062126</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-12 20:50:57</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>104753.3050171104</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-09 04:40:34</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>99224.620291181</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-21 17:55:00</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>23495.483284224</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 08:22:28</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>64699.136242586996</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:47:19</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>48572.2214068028</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 15:06:16</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>170671.7130733536</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:23:05</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>200230.62454986</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24 17:08:04</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>234745.27086876464</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-15 20:00:06</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>224306.86610140197</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-04 03:59:06</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>106784.2472752224</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-27 17:44:53</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>179941.669147122</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-14 21:13:52</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>80105.5212933888</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-11 16:17:39</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>110340.74972543851</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:19:32</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>97745.4001933332</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:10:46</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>66418.7527752094</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03 05:47:44</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>139413.13873754893</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:05:03</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>10408.794507441002</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 21:03:13</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>57073.840982442896</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-12 13:12:26</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>19382.96627551</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09 10:47:26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>98578.45051857</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-28 16:34:51</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>211824.00006395628</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-07 02:17:08</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>58258.0205823672</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 17:32:43</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>79013.294466696</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-04 20:45:42</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>123570.19787205601</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27 00:30:59</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>235189.08084613</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:59:15</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>160233.8287503656</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 18:41:41</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>153865.8969085798</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-14 21:44:58</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>74854.7117620488</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18 01:36:01</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>38852.8216956448</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-11 06:08:47</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>126033.10821117701</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-23 12:47:52</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>8683.6139595635</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:28:40</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>84526.48870991009</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-23 15:11:23</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>62001.539086132805</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23 12:10:23</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>106259.32295359709</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-04 13:53:56</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>210680.7223689896</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-15 07:03:07</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>293280.8977793574</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-04 17:43:27</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>179566.3569808053</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:42:52</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>189609.9436762765</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-11 14:29:27</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>124082.964693268</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:34:23</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>136127.0380696884</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:04:33</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>218356.0586658495</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04 13:37:57</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>219207.61960503447</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 17:43:03</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>217985.85922548157</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-03 19:27:37</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>100769.9744104626</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-10 19:05:37</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>52503.2332897376</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 06:31:50</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>26811.847522278</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-21 09:28:46</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>220542.52142384602</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 12:08:58</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>156882.83731498898</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:40:53</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>8686.946900771998</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 07:50:49</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>162366.6646785122</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-12 07:48:49</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>21889.3240949292</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-26 20:34:10</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>146250.793535875</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 01:40:57</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>25388.41384704</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:22:48</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>177078.89194314796</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07 02:31:13</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>7815.176329999999</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24 00:58:59</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>156223.96842685</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-20 22:33:42</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>81907.763898285</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:34:44</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>46890.2419242147</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-06 21:30:01</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>77081.9243779482</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 19:56:55</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>200667.81086513336</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-15 14:08:59</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>5759.939823422401</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 15:24:28</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>41414.1796452306</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-01 19:35:15</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>105116.6882658724</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-24 08:54:04</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>46552.30066044</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-23 18:40:20</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>106747.519653944</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 02:25:47</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>24658.588079243993</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-04 11:00:24</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>78592.9991714416</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-07 09:59:44</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>121913.165423484</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:53:52</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>11238.0386291712</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:09:49</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>102805.91931391381</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-12 20:48:38</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>126214.5115078225</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:53:44</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>130190.89249179121</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 04:42:28</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>147406.8013538497</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-12 01:43:09</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>349877.0672951616</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-09 17:14:16</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>173847.64182755852</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-05 09:56:26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>174044.57088871198</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:37:24</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>38501.2850950452</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23 03:25:47</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>156353.71318286724</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:30:46</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>91837.67765383891</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 11:07:05</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>138061.08943164797</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07 03:33:39</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>12674.393411592</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-01 11:47:35</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>33861.553695072005</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:40:02</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>75949.29223180379</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24 03:06:28</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>124307.447051016</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-03 15:38:11</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>3585.008163672</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 14:34:52</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>196860.03968003378</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-24 01:02:18</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>128739.23710441921</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:04:01</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>16001.3519943912</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09 17:18:20</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>74465.97261943841</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-17 15:38:39</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>204996.60538256535</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23 23:59:27</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>63579.90892428</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 19:02:14</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>11434.831244877601</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-08 00:13:45</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>35589.7915334076</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18 19:38:37</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>122444.139814591</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-27 09:53:28</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>119282.41132104959</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-03 10:40:01</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>198966.8113390672</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:35:41</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>97810.6458970115</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-08 04:07:49</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>110942.86201568</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 20:40:38</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>206272.02147019652</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-15 01:12:51</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>219648.05221669836</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-01 03:42:32</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>201916.46101624996</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 17:41:42</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>209945.244418226</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-16 16:54:23</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>139501.66855009217</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-07 13:52:44</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>68172.6839079216</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 08:14:55</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>38875.1999659824</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:52:17</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>16755.213429266</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-02 05:41:40</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>177224.7308761522</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-16 12:48:12</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>15511.6794624256</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-03 17:13:14</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>40549.063780712</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03 20:06:09</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>94442.60993175118</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10 09:15:32</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>76337.49753045001</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25 08:47:52</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>248256.17907859507</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-12 14:43:49</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>198347.4794596176</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-22 12:21:10</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>105328.156933935</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-13 08:27:06</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>55350.67344612299</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-17 16:33:32</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>42438.005316104995</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-12 02:23:13</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>117645.48526174879</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 13:58:11</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>109680.53837567999</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:38:54</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>45437.514760665596</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13 19:51:24</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>30506.599638912</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09 05:27:39</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>62009.5014040837</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:05:12</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>71208.7190298932</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09 00:05:28</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>136583.88575720642</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:20:40</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>175130.1827390256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-23 04:33:59</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>101208.9037327872</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-06 18:15:24</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>199640.6642005356</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19 11:18:02</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>96000.5392655764</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-07 08:21:46</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>10674.540677085402</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-05 19:42:20</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>79496.0485279372</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:42:08</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>39535.9374318552</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-03 18:57:59</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>117663.91248653998</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17 03:13:19</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>124842.1227118983</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18 13:05:18</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>198831.997656456</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-23 14:34:01</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>99453.6579800076</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-09 22:56:35</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>28920.6354304824</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18 13:22:52</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>124710.89275359659</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07 04:49:41</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>14340.3598954908</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25 12:12:03</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>97924.12514364239</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12 01:43:31</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>68205.68489869201</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:54:33</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>116051.1235859696</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-03 03:29:30</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>7412.240008152001</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-11 00:41:19</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>23430.4347204096</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-12 20:22:13</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>92507.68943707149</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:02:15</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>19314.8523351952</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:49:27</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>90474.595616384</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:09:42</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>95437.6058504562</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-12 06:55:29</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>122624.63697212821</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 11:31:59</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>50773.8010373844</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:35:58</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>118772.23248760882</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:38:59</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>108993.2313701112</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-06 03:21:29</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>47875.369244784</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-18 08:04:42</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>183648.5501563944</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-25 20:06:25</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>33444.729637149605</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 09:20:43</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>226431.2205034576</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07 06:32:28</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>123126.64089601442</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 18:17:33</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>188735.58185030642</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26 21:17:54</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>131369.7923363975</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 07:57:04</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>88337.357091159</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-27 19:49:23</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>208008.899271563</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-28 03:23:45</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>62540.26547502241</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-12 07:47:34</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>287670.0594601443</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:46:19</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>117490.12973824439</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:25:25</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>1796.781522042</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-04 13:02:34</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>9183.264795635701</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-18 13:22:52</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>31506.600399624</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-07 18:02:55</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>123305.9834838512</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-17 07:32:04</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>62366.5224263704</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 00:57:06</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>134841.93173270643</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-13 22:43:00</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>54258.472848236794</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 07:01:44</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>92424.10618114079</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-10 16:41:48</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>95238.6577243778</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01 20:25:32</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>21187.453352256</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16 10:01:30</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>87012.52232905121</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:20:01</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>22229.094217902002</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-10 02:55:13</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>202384.32547872</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-07 20:29:35</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>451648.135820556</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:54:03</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>4139.843533005999</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 08:20:45</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>180579.59425349996</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-13 03:52:07</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>105575.67537940391</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 17:35:23</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>159135.96764054758</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10 17:01:57</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>107580.83434514471</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10 01:44:11</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>134321.477480008</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19 22:57:20</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>164743.40877613318</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 13:42:15</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>107677.92134315732</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24 08:33:10</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>166687.08488026558</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19 17:59:31</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>76141.96249621849</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18 13:47:24</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>115118.42970305879</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-13 08:46:29</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>62806.822807165496</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10 18:48:30</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>109580.9485835559</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-21 05:06:19</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>245717.04516053598</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-24 14:56:32</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>116740.22056826799</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 15:23:17</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>139373.22182853098</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04 04:00:09</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>98119.699257734</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13 06:59:59</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>198535.1495453446</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:13:51</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>55039.0718265</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-13 16:27:39</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>14302.6622362624</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15 22:48:39</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>6299.215942438601</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 23:06:20</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>271032.1545866931</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:44:52</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>112812.996648144</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-15 15:39:32</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>30497.478292990807</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 04:22:00</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>214871.64277883654</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21 14:47:16</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>24313.9079898826</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17 18:56:39</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>185775.53728801318</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21 18:03:38</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>220192.3031263724</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 06:37:28</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>310489.6363261938</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-25 02:05:42</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>68681.5500855042</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:59:37</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>40276.1100177632</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:33:30</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>195995.1574224276</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02 03:19:36</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>113321.29630205999</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 02:41:09</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>295545.310354601</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:29:31</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>134980.96014460438</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-05 16:18:09</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>290734.6656060804</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-02 04:03:28</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>206266.76192088</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-05 18:05:51</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>127590.7426595712</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-27 19:12:53</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>134925.76503753</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-10 21:56:54</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>210253.33465610884</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-10 19:23:54</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>174443.6940219792</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:31:35</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>88675.65385761601</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-25 16:42:37</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>111009.27192914499</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23 11:09:28</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>131679.404346962</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-08 11:01:27</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>34662.680386236</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-25 08:17:53</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>73475.74609689601</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-20 15:44:57</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>21888.591569279997</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 00:39:05</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>10054.0703867136</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09 13:57:18</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>150314.606476052</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09 12:48:11</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>225652.36844040657</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:04:01</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>78357.4312670644</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-25 19:40:11</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>187691.511559008</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24 14:53:22</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>55992.9496842339</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24 21:34:28</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>107031.3845877584</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:22:49</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>15438.8291531436</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-21 05:44:49</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>140003.89374606797</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-26 16:21:12</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
+          <t>106686.27279933</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-19 19:42:23</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>78092.21969422999</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 01:54:39</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr">
+        <is>
+          <t>27940.527476579202</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-19 04:12:31</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>88045.79526305759</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 13:16:16</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr">
+        <is>
+          <t>107498.16391831201</t>
+        </is>
+      </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02 07:08:00</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>190667.3622863968</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-02 05:22:52</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr">
+        <is>
+          <t>64131.72821852761</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-20 03:29:05</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>165935.97219371397</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-27 05:54:31</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr">
+        <is>
+          <t>178214.75898683196</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:35:15</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>132283.9506324549</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-06 07:50:26</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr">
+        <is>
+          <t>97306.43419515199</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 10:14:32</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>200812.2104731252</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07 03:19:34</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr">
+        <is>
+          <t>132201.7724103521</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17 02:33:33</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>91408.8523295376</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-17 14:22:49</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>138663.8633859178</t>
+        </is>
+      </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:08:56</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>219830.03371520722</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05 17:23:11</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>189197.2802302168</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-21 23:01:53</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>145421.8073139888</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-25 02:16:27</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>299395.62859659</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11 05:35:37</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>147031.35854673386</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-02 07:38:55</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>46448.42239232</t>
+        </is>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-04 16:13:11</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>76570.374324576</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05 15:30:54</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="inlineStr">
+        <is>
+          <t>114481.13846677759</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20 06:50:31</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>7620.324100993999</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-04 06:35:25</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="inlineStr">
+        <is>
+          <t>81188.6006248318</t>
+        </is>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19 19:45:56</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>193330.94022508804</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-08 08:03:56</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="inlineStr">
+        <is>
+          <t>82889.163232416</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:07:24</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>255526.53959653337</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-12 15:49:22</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>241865.8266415853</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 02:44:46</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>115030.19159378798</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26 00:28:57</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="inlineStr">
+        <is>
+          <t>109387.6364793584</t>
+        </is>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 06:56:09</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>35345.9106016608</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-22 03:30:02</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>70751.26096803</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27 23:48:48</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>166990.62479225223</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-18 07:15:59</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="inlineStr">
+        <is>
+          <t>80036.6887635588</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-21 13:07:13</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>116164.43957880003</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:07:33</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>181572.1178920462</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:39:02</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>20306.505845289597</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10 02:45:09</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>256341.5123828616</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:19:49</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>47442.4441363536</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08 05:12:15</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>360239.3927139436</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:22:05</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>221123.83504220503</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:45:26</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>1757.40001164</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:34:34</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>84695.8677933538</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-16 00:29:05</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="inlineStr">
+        <is>
+          <t>32010.2107500812</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-15 08:05:16</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>131428.5589985082</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28 05:04:19</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="inlineStr">
+        <is>
+          <t>61773.482075240005</t>
+        </is>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-06 09:43:04</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>54432.9540804672</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-03 21:11:47</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="inlineStr">
+        <is>
+          <t>181770.2791253055</t>
+        </is>
+      </c>
+      <c r="C323" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:35:51</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>97204.61972250638</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-08 14:41:44</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="inlineStr">
+        <is>
+          <t>204925.9579730688</t>
+        </is>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:17:34</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>54576.685042499994</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-09 03:11:14</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="inlineStr">
+        <is>
+          <t>86456.2764858018</t>
+        </is>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28 05:48:15</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>109280.7190118952</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-25 23:14:54</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="inlineStr">
+        <is>
+          <t>158277.00792422</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-22 20:30:16</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>140993.87270605803</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14 22:35:33</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="inlineStr">
+        <is>
+          <t>213816.73783517323</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:41:32</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>65271.45397678499</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-14 07:43:49</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>205214.22500141338</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:25:57</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>93587.06779086139</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-19 11:09:56</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>31874.471727</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15 18:04:37</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>121733.69700270239</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-07 11:23:39</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>173439.21771374939</t>
+        </is>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:38:20</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>72781.99307643269</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19 21:01:49</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>124284.61762809439</t>
+        </is>
+      </c>
+      <c r="C339" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:47:52</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>60697.4873219658</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-07 16:34:42</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="inlineStr">
+        <is>
+          <t>9434.8366898368</t>
+        </is>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-14 12:00:39</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>144596.5246326895</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-07 15:47:39</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="inlineStr">
+        <is>
+          <t>124259.52612573499</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03 19:06:44</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>94315.2242383455</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-05 02:46:25</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="inlineStr">
+        <is>
+          <t>100169.986666798</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02 09:06:00</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>64475.9098088028</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28 18:52:30</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="inlineStr">
+        <is>
+          <t>51929.498529963996</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02 15:08:14</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>6212.5145555949</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-17 19:11:01</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="inlineStr">
+        <is>
+          <t>22368.007520474</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:32:21</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>86575.55056390149</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15 00:11:22</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="inlineStr">
+        <is>
+          <t>208185.54665882097</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-17 23:58:17</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>117431.359932908</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:09:49</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="inlineStr">
+        <is>
+          <t>35936.6149514808</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13 01:33:31</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>17293.386466554</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19 17:52:24</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>4138.512821219</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-19 00:42:28</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>6807.2610544245</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-08 07:41:53</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>218898.44959956303</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 20:44:03</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>85696.6174584492</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-20 17:24:51</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>72348.71305493281</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-26 18:21:26</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>130236.780983478</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-14 12:14:36</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>192694.62974723638</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-28 07:53:22</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>54651.751090757105</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-17 14:23:00</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="inlineStr">
+        <is>
+          <t>197205.16811043996</t>
+        </is>
+      </c>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-12 00:07:51</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>116182.1163957128</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03 17:00:55</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="inlineStr">
+        <is>
+          <t>31442.473688504404</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 22:07:14</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>131659.47763082</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-28 14:27:23</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="inlineStr">
+        <is>
+          <t>123962.62461860491</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026-12-21 17:30:50</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>123436.33233644819</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-05 13:05:44</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="inlineStr">
+        <is>
+          <t>134362.93096809599</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D369" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:41:52</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>145966.8263255488</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26 03:22:24</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="inlineStr">
+        <is>
+          <t>139751.81334066132</t>
+        </is>
+      </c>
+      <c r="C371" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D371" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-20 11:45:36</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>219699.83881702082</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-26 23:12:28</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="inlineStr">
+        <is>
+          <t>202141.56949862398</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-04 02:23:57</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>18200.421772588797</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="3" t="inlineStr">
+        <is>
+          <t>2026-12-13 11:29:21</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="inlineStr">
+        <is>
+          <t>55098.156177216006</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D375" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03 16:46:51</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>115277.09721472651</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:57:54</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>73198.5622878629</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18 09:02:25</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>13601.307013528201</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-15 05:56:23</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>68946.3511642395</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:49:04</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>60138.66172536599</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de debito</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-10 04:58:06</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>196717.27890783802</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:59:37</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>172305.0467049078</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-27 03:52:25</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>150703.0899758438</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21 07:31:45</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>202497.62555207923</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-01 18:31:27</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="inlineStr">
+        <is>
+          <t>19852.1386663556</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>Cheque</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09 23:52:24</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>134710.818283275</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-19 14:39:30</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="inlineStr">
+        <is>
+          <t>153831.53605257522</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D387" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-19 07:31:23</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>36158.973002239494</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 03:39:22</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="inlineStr">
+        <is>
+          <t>63933.62145984</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D389" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-24 17:17:37</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>246387.88995632902</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-14 14:48:25</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="inlineStr">
+        <is>
+          <t>270878.9858346428</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-16 06:31:27</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>138160.9600059588</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-21 20:43:11</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr">
+        <is>
+          <t>168051.9651441738</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22 12:18:32</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>34853.613790953605</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>Transferencia</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-28 04:04:24</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr">
+        <is>
+          <t>225937.446402372</t>
+        </is>
+      </c>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27 03:47:13</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>192035.316368577</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-18 18:56:38</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="inlineStr">
+        <is>
+          <t>QR</t>
+        </is>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19 00:00:54</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 00:33:35</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>-30360.0</t>
+        </is>
+      </c>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19 01:20:31</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>-303600.0</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 01:21:49</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="C401" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19 01:22:24</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>-2760.0</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 02:00:45</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="C403" s="3" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>koch</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-19 02:16:24</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>Tarjeta de credito</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>koch</t>
         </is>
       </c>
     </row>
